--- a/rental-analysis-app/Kinto Fleet_3-19-26.xlsx
+++ b/rental-analysis-app/Kinto Fleet_3-19-26.xlsx
@@ -5,19 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fletchj\VS Studio\rental-analysis-app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fletchj\VS Studio\Kinto\rental-analysis-app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D4C1047-1514-4FEC-B498-419B54B5D673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19FD1E4E-C227-40FD-8C84-69C910F64AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22050" yWindow="-17520" windowWidth="19140" windowHeight="13680" firstSheet="1" activeTab="1" xr2:uid="{1CF60188-9169-40FA-8003-611196E33864}"/>
+    <workbookView xWindow="13770" yWindow="-21720" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="2" xr2:uid="{1CF60188-9169-40FA-8003-611196E33864}"/>
   </bookViews>
   <sheets>
     <sheet name="Dep TCCI" sheetId="2" state="hidden" r:id="rId1"/>
     <sheet name="data" sheetId="1" r:id="rId2"/>
+    <sheet name="active%" sheetId="3" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">data!$A$1:$Q$84</definedName>
@@ -1014,7 +1015,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="263">
   <si>
     <t>Year</t>
   </si>
@@ -1755,19 +1756,68 @@
   </si>
   <si>
     <t>Onboarded</t>
+  </si>
+  <si>
+    <t>Total Fleet</t>
+  </si>
+  <si>
+    <t>Active Fleet</t>
+  </si>
+  <si>
+    <t>Down Fleet</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>February</t>
+  </si>
+  <si>
+    <t>January</t>
+  </si>
+  <si>
+    <t>December</t>
+  </si>
+  <si>
+    <t>November</t>
+  </si>
+  <si>
+    <t>October</t>
+  </si>
+  <si>
+    <t>September</t>
+  </si>
+  <si>
+    <t>August</t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>Month</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="169" formatCode="[$-409]mmmm"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1956,6 +2006,12 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="40">
@@ -2181,7 +2237,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -2296,6 +2352,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2346,7 +2417,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2427,9 +2498,14 @@
     <xf numFmtId="9" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="45" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="46" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="44" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="47">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -7595,12 +7671,12 @@
       </c>
       <c r="O5" s="18">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P5" s="18"/>
       <c r="Q5" s="3">
         <f ca="1">(YEAR(O5) - YEAR(M5)) * 12 + MONTH(O5) - MONTH(M5) + 1</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R5" s="3" t="str">
         <f>VLOOKUP(I5, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -7614,13 +7690,13 @@
       <c r="U5" s="9"/>
       <c r="V5" s="8">
         <f ca="1">L5-(C5*Q5)</f>
-        <v>27476.283333333333</v>
+        <v>26845.354166666664</v>
       </c>
       <c r="W5" s="3"/>
       <c r="X5" s="11"/>
       <c r="Z5" s="12">
         <f ca="1">Q5*C5</f>
-        <v>17666.01666666667</v>
+        <v>18296.945833333339</v>
       </c>
       <c r="AA5" s="12">
         <f>(J5-F5)/24</f>
@@ -7628,11 +7704,11 @@
       </c>
       <c r="AB5" s="12">
         <f ca="1">+AA5*Q5</f>
-        <v>18213.661666666663</v>
+        <v>18864.149583333332</v>
       </c>
       <c r="AC5" s="12">
         <f ca="1">+Z5-AB5</f>
-        <v>-547.64499999999316</v>
+        <v>-567.20374999999331</v>
       </c>
     </row>
     <row r="6" spans="2:29" x14ac:dyDescent="0.3">
@@ -8070,12 +8146,12 @@
       </c>
       <c r="O13" s="18">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P13" s="18"/>
       <c r="Q13" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R13" s="3" t="str">
         <f>VLOOKUP(I13, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -8089,13 +8165,13 @@
       <c r="U13" s="9"/>
       <c r="V13" s="8">
         <f ca="1">L13-(C13*Q13)</f>
-        <v>27476.283333333333</v>
+        <v>26845.354166666664</v>
       </c>
       <c r="W13" s="3"/>
       <c r="X13" s="11"/>
       <c r="Z13" s="12">
         <f ca="1">Q13*C13</f>
-        <v>17666.01666666667</v>
+        <v>18296.945833333339</v>
       </c>
       <c r="AA13" s="12">
         <f t="shared" si="4"/>
@@ -8103,11 +8179,11 @@
       </c>
       <c r="AB13" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>14713.666666666672</v>
+        <v>15239.154761904767</v>
       </c>
       <c r="AC13" s="12">
         <f t="shared" ca="1" si="2"/>
-        <v>2952.3499999999985</v>
+        <v>3057.7910714285717</v>
       </c>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.3">
@@ -8194,12 +8270,12 @@
       </c>
       <c r="O16" s="18">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P16" s="18"/>
       <c r="Q16" s="3">
         <f t="shared" ref="Q16:Q20" ca="1" si="6">(YEAR(O16) - YEAR(M16)) * 12 + MONTH(O16) - MONTH(M16) + 1</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R16" s="3" t="str">
         <f>VLOOKUP(I16, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -8213,13 +8289,13 @@
       <c r="U16" s="9"/>
       <c r="V16" s="8">
         <f ca="1">L16-(C16*Q16)</f>
-        <v>26645.504999999997</v>
+        <v>25806.881249999999</v>
       </c>
       <c r="W16" s="3"/>
       <c r="X16" s="11"/>
       <c r="Z16" s="12">
         <f ca="1">Q16*C16</f>
-        <v>23481.465000000004</v>
+        <v>24320.088750000003</v>
       </c>
       <c r="AB16" s="12"/>
       <c r="AC16" s="12"/>
@@ -9565,12 +9641,12 @@
       </c>
       <c r="O35" s="18">
         <f t="shared" ref="O35:O41" ca="1" si="16">TODAY()</f>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P35" s="18"/>
       <c r="Q35" s="3">
         <f t="shared" ref="Q35:Q41" ca="1" si="17">(YEAR(O35) - YEAR(M35)) * 12 + MONTH(O35) - MONTH(M35) + 1</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R35" s="3" t="str">
         <f>VLOOKUP(I35, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -9584,13 +9660,13 @@
       <c r="U35" s="9"/>
       <c r="V35" s="8">
         <f t="shared" ref="V35:V41" ca="1" si="18">L35-(C35*Q35)</f>
-        <v>33032.708333333336</v>
+        <v>31959.4375</v>
       </c>
       <c r="W35" s="3"/>
       <c r="X35" s="11"/>
       <c r="Z35" s="12">
         <f t="shared" ref="Z35:Z41" ca="1" si="19">Q35*C35</f>
-        <v>15025.791666666666</v>
+        <v>16099.062499999998</v>
       </c>
       <c r="AA35" s="12">
         <f>(J35-$F$35)/24</f>
@@ -9598,11 +9674,11 @@
       </c>
       <c r="AB35" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>13690.833333333332</v>
+        <v>14668.75</v>
       </c>
       <c r="AC35" s="12">
         <f t="shared" ca="1" si="2"/>
-        <v>1334.9583333333339</v>
+        <v>1430.3124999999982</v>
       </c>
     </row>
     <row r="36" spans="2:29" x14ac:dyDescent="0.3">
@@ -9648,12 +9724,12 @@
       </c>
       <c r="O36" s="18">
         <f t="shared" ca="1" si="16"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P36" s="18"/>
       <c r="Q36" s="3">
         <f t="shared" ca="1" si="17"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R36" s="3" t="str">
         <f>VLOOKUP(I36, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -9667,13 +9743,13 @@
       <c r="U36" s="9"/>
       <c r="V36" s="8">
         <f t="shared" ca="1" si="18"/>
-        <v>33032.708333333336</v>
+        <v>31959.4375</v>
       </c>
       <c r="W36" s="3"/>
       <c r="X36" s="11"/>
       <c r="Z36" s="12">
         <f t="shared" ca="1" si="19"/>
-        <v>15025.791666666666</v>
+        <v>16099.062499999998</v>
       </c>
       <c r="AA36" s="12">
         <f t="shared" ref="AA36:AA41" si="21">(J36-$F$35)/24</f>
@@ -9681,11 +9757,11 @@
       </c>
       <c r="AB36" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>13690.833333333332</v>
+        <v>14668.75</v>
       </c>
       <c r="AC36" s="12">
         <f t="shared" ca="1" si="2"/>
-        <v>1334.9583333333339</v>
+        <v>1430.3124999999982</v>
       </c>
     </row>
     <row r="37" spans="2:29" x14ac:dyDescent="0.3">
@@ -9731,12 +9807,12 @@
       </c>
       <c r="O37" s="18">
         <f t="shared" ca="1" si="16"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P37" s="18"/>
       <c r="Q37" s="3">
         <f t="shared" ca="1" si="17"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R37" s="3" t="str">
         <f>VLOOKUP(I37, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -9750,13 +9826,13 @@
       <c r="U37" s="9"/>
       <c r="V37" s="8">
         <f t="shared" ca="1" si="18"/>
-        <v>33032.708333333336</v>
+        <v>31959.4375</v>
       </c>
       <c r="W37" s="3"/>
       <c r="X37" s="11"/>
       <c r="Z37" s="12">
         <f t="shared" ca="1" si="19"/>
-        <v>15025.791666666666</v>
+        <v>16099.062499999998</v>
       </c>
       <c r="AA37" s="12">
         <f t="shared" si="21"/>
@@ -9764,11 +9840,11 @@
       </c>
       <c r="AB37" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>13690.833333333332</v>
+        <v>14668.75</v>
       </c>
       <c r="AC37" s="12">
         <f t="shared" ca="1" si="2"/>
-        <v>1334.9583333333339</v>
+        <v>1430.3124999999982</v>
       </c>
     </row>
     <row r="38" spans="2:29" x14ac:dyDescent="0.3">
@@ -9814,12 +9890,12 @@
       </c>
       <c r="O38" s="18">
         <f t="shared" ca="1" si="16"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P38" s="18"/>
       <c r="Q38" s="3">
         <f t="shared" ca="1" si="17"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R38" s="3" t="str">
         <f>VLOOKUP(I38, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -9833,13 +9909,13 @@
       <c r="U38" s="9"/>
       <c r="V38" s="8">
         <f t="shared" ca="1" si="18"/>
-        <v>33032.708333333336</v>
+        <v>31959.4375</v>
       </c>
       <c r="W38" s="3"/>
       <c r="X38" s="11"/>
       <c r="Z38" s="12">
         <f t="shared" ca="1" si="19"/>
-        <v>15025.791666666666</v>
+        <v>16099.062499999998</v>
       </c>
       <c r="AA38" s="12">
         <f t="shared" si="21"/>
@@ -9847,11 +9923,11 @@
       </c>
       <c r="AB38" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>13690.833333333332</v>
+        <v>14668.75</v>
       </c>
       <c r="AC38" s="12">
         <f t="shared" ca="1" si="2"/>
-        <v>1334.9583333333339</v>
+        <v>1430.3124999999982</v>
       </c>
     </row>
     <row r="39" spans="2:29" x14ac:dyDescent="0.3">
@@ -9897,12 +9973,12 @@
       </c>
       <c r="O39" s="18">
         <f t="shared" ca="1" si="16"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P39" s="18"/>
       <c r="Q39" s="3">
         <f t="shared" ca="1" si="17"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R39" s="3" t="str">
         <f>VLOOKUP(I39, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -9916,13 +9992,13 @@
       <c r="U39" s="9"/>
       <c r="V39" s="8">
         <f t="shared" ca="1" si="18"/>
-        <v>33032.708333333336</v>
+        <v>31959.4375</v>
       </c>
       <c r="W39" s="3"/>
       <c r="X39" s="11"/>
       <c r="Z39" s="12">
         <f t="shared" ca="1" si="19"/>
-        <v>15025.791666666666</v>
+        <v>16099.062499999998</v>
       </c>
       <c r="AA39" s="12">
         <f t="shared" si="21"/>
@@ -9930,11 +10006,11 @@
       </c>
       <c r="AB39" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>13690.833333333332</v>
+        <v>14668.75</v>
       </c>
       <c r="AC39" s="12">
         <f t="shared" ca="1" si="2"/>
-        <v>1334.9583333333339</v>
+        <v>1430.3124999999982</v>
       </c>
     </row>
     <row r="40" spans="2:29" x14ac:dyDescent="0.3">
@@ -9980,12 +10056,12 @@
       </c>
       <c r="O40" s="18">
         <f t="shared" ca="1" si="16"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P40" s="18"/>
       <c r="Q40" s="3">
         <f t="shared" ca="1" si="17"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R40" s="3" t="str">
         <f>VLOOKUP(I40, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -9999,13 +10075,13 @@
       <c r="U40" s="9"/>
       <c r="V40" s="8">
         <f t="shared" ca="1" si="18"/>
-        <v>33032.708333333336</v>
+        <v>31959.4375</v>
       </c>
       <c r="W40" s="3"/>
       <c r="X40" s="11"/>
       <c r="Z40" s="12">
         <f t="shared" ca="1" si="19"/>
-        <v>15025.791666666666</v>
+        <v>16099.062499999998</v>
       </c>
       <c r="AA40" s="12">
         <f t="shared" si="21"/>
@@ -10013,11 +10089,11 @@
       </c>
       <c r="AB40" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>13690.833333333332</v>
+        <v>14668.75</v>
       </c>
       <c r="AC40" s="12">
         <f t="shared" ca="1" si="2"/>
-        <v>1334.9583333333339</v>
+        <v>1430.3124999999982</v>
       </c>
     </row>
     <row r="41" spans="2:29" x14ac:dyDescent="0.3">
@@ -10063,12 +10139,12 @@
       </c>
       <c r="O41" s="18">
         <f t="shared" ca="1" si="16"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P41" s="18"/>
       <c r="Q41" s="3">
         <f t="shared" ca="1" si="17"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R41" s="3" t="str">
         <f>VLOOKUP(I41, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -10082,13 +10158,13 @@
       <c r="U41" s="9"/>
       <c r="V41" s="8">
         <f t="shared" ca="1" si="18"/>
-        <v>34105.979166666672</v>
+        <v>33032.708333333336</v>
       </c>
       <c r="W41" s="3"/>
       <c r="X41" s="11"/>
       <c r="Z41" s="12">
         <f t="shared" ca="1" si="19"/>
-        <v>13952.520833333332</v>
+        <v>15025.791666666666</v>
       </c>
       <c r="AA41" s="12">
         <f t="shared" si="21"/>
@@ -10096,11 +10172,11 @@
       </c>
       <c r="AB41" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>12712.916666666666</v>
+        <v>13690.833333333332</v>
       </c>
       <c r="AC41" s="12">
         <f t="shared" ca="1" si="2"/>
-        <v>1239.6041666666661</v>
+        <v>1334.9583333333339</v>
       </c>
     </row>
     <row r="42" spans="2:29" x14ac:dyDescent="0.3">
@@ -10209,12 +10285,12 @@
       </c>
       <c r="O44" s="18">
         <f t="shared" ref="O44:O51" ca="1" si="24">TODAY()</f>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P44" s="18"/>
       <c r="Q44" s="3">
         <f t="shared" ref="Q44:Q51" ca="1" si="25">(YEAR(O44) - YEAR(M44)) * 12 + MONTH(O44) - MONTH(M44) + 1</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R44" s="3" t="str">
         <f>VLOOKUP(I44, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -10228,13 +10304,13 @@
       <c r="U44" s="9"/>
       <c r="V44" s="8">
         <f t="shared" ref="V44:V51" ca="1" si="26">L44-(C44*Q44)</f>
-        <v>33647.979166666672</v>
+        <v>32583.181250000001</v>
       </c>
       <c r="W44" s="3"/>
       <c r="X44" s="11"/>
       <c r="Z44" s="12">
         <f t="shared" ref="Z44:Z51" ca="1" si="27">Q44*C44</f>
-        <v>14907.170833333334</v>
+        <v>15971.96875</v>
       </c>
       <c r="AA44" s="12">
         <f>(J44-$F$44)/24</f>
@@ -10242,11 +10318,11 @@
       </c>
       <c r="AB44" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>13558.416666666668</v>
+        <v>14526.875</v>
       </c>
       <c r="AC44" s="12">
         <f t="shared" ca="1" si="2"/>
-        <v>1348.7541666666657</v>
+        <v>1445.09375</v>
       </c>
     </row>
     <row r="45" spans="2:29" x14ac:dyDescent="0.3">
@@ -10292,12 +10368,12 @@
       </c>
       <c r="O45" s="18">
         <f t="shared" ca="1" si="24"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P45" s="18"/>
       <c r="Q45" s="3">
         <f t="shared" ca="1" si="25"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R45" s="3" t="str">
         <f>VLOOKUP(I45, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -10311,13 +10387,13 @@
       <c r="U45" s="9"/>
       <c r="V45" s="8">
         <f t="shared" ca="1" si="26"/>
-        <v>34712.777083333334</v>
+        <v>33647.979166666672</v>
       </c>
       <c r="W45" s="3"/>
       <c r="X45" s="11"/>
       <c r="Z45" s="12">
         <f t="shared" ca="1" si="27"/>
-        <v>13842.372916666667</v>
+        <v>14907.170833333334</v>
       </c>
       <c r="AA45" s="12">
         <f t="shared" ref="AA45:AA51" si="29">(J45-$F$44)/24</f>
@@ -10325,11 +10401,11 @@
       </c>
       <c r="AB45" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>12589.958333333334</v>
+        <v>13558.416666666668</v>
       </c>
       <c r="AC45" s="12">
         <f t="shared" ca="1" si="2"/>
-        <v>1252.4145833333332</v>
+        <v>1348.7541666666657</v>
       </c>
     </row>
     <row r="46" spans="2:29" x14ac:dyDescent="0.3">
@@ -10375,12 +10451,12 @@
       </c>
       <c r="O46" s="18">
         <f t="shared" ca="1" si="24"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P46" s="18"/>
       <c r="Q46" s="3">
         <f t="shared" ca="1" si="25"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R46" s="3" t="str">
         <f>VLOOKUP(I46, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -10394,13 +10470,13 @@
       <c r="U46" s="9"/>
       <c r="V46" s="8">
         <f t="shared" ca="1" si="26"/>
-        <v>33647.979166666672</v>
+        <v>32583.181250000001</v>
       </c>
       <c r="W46" s="3"/>
       <c r="X46" s="11"/>
       <c r="Z46" s="12">
         <f t="shared" ca="1" si="27"/>
-        <v>14907.170833333334</v>
+        <v>15971.96875</v>
       </c>
       <c r="AA46" s="12">
         <f t="shared" si="29"/>
@@ -10408,11 +10484,11 @@
       </c>
       <c r="AB46" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>13558.416666666668</v>
+        <v>14526.875</v>
       </c>
       <c r="AC46" s="12">
         <f t="shared" ca="1" si="2"/>
-        <v>1348.7541666666657</v>
+        <v>1445.09375</v>
       </c>
     </row>
     <row r="47" spans="2:29" x14ac:dyDescent="0.3">
@@ -10458,12 +10534,12 @@
       </c>
       <c r="O47" s="18">
         <f t="shared" ca="1" si="24"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P47" s="18"/>
       <c r="Q47" s="3">
         <f t="shared" ca="1" si="25"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R47" s="3" t="str">
         <f>VLOOKUP(I47, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -10477,13 +10553,13 @@
       <c r="U47" s="9"/>
       <c r="V47" s="8">
         <f t="shared" ca="1" si="26"/>
-        <v>33647.979166666672</v>
+        <v>32583.181250000001</v>
       </c>
       <c r="W47" s="3"/>
       <c r="X47" s="11"/>
       <c r="Z47" s="12">
         <f t="shared" ca="1" si="27"/>
-        <v>14907.170833333334</v>
+        <v>15971.96875</v>
       </c>
       <c r="AA47" s="12">
         <f t="shared" si="29"/>
@@ -10491,11 +10567,11 @@
       </c>
       <c r="AB47" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>13558.416666666668</v>
+        <v>14526.875</v>
       </c>
       <c r="AC47" s="12">
         <f t="shared" ca="1" si="2"/>
-        <v>1348.7541666666657</v>
+        <v>1445.09375</v>
       </c>
     </row>
     <row r="48" spans="2:29" x14ac:dyDescent="0.3">
@@ -10541,12 +10617,12 @@
       </c>
       <c r="O48" s="18">
         <f t="shared" ca="1" si="24"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P48" s="18"/>
       <c r="Q48" s="3">
         <f t="shared" ca="1" si="25"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R48" s="3" t="str">
         <f>VLOOKUP(I48, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -10560,13 +10636,13 @@
       <c r="U48" s="9"/>
       <c r="V48" s="8">
         <f t="shared" ca="1" si="26"/>
-        <v>33647.979166666672</v>
+        <v>32583.181250000001</v>
       </c>
       <c r="W48" s="3"/>
       <c r="X48" s="11"/>
       <c r="Z48" s="12">
         <f t="shared" ca="1" si="27"/>
-        <v>14907.170833333334</v>
+        <v>15971.96875</v>
       </c>
       <c r="AA48" s="12">
         <f t="shared" si="29"/>
@@ -10574,11 +10650,11 @@
       </c>
       <c r="AB48" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>13558.416666666668</v>
+        <v>14526.875</v>
       </c>
       <c r="AC48" s="12">
         <f t="shared" ca="1" si="2"/>
-        <v>1348.7541666666657</v>
+        <v>1445.09375</v>
       </c>
     </row>
     <row r="49" spans="2:29" x14ac:dyDescent="0.3">
@@ -10624,12 +10700,12 @@
       </c>
       <c r="O49" s="18">
         <f t="shared" ca="1" si="24"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P49" s="18"/>
       <c r="Q49" s="3">
         <f t="shared" ca="1" si="25"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R49" s="3" t="str">
         <f>VLOOKUP(I49, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -10643,13 +10719,13 @@
       <c r="U49" s="9"/>
       <c r="V49" s="8">
         <f t="shared" ca="1" si="26"/>
-        <v>33647.979166666672</v>
+        <v>32583.181250000001</v>
       </c>
       <c r="W49" s="3"/>
       <c r="X49" s="11"/>
       <c r="Z49" s="12">
         <f t="shared" ca="1" si="27"/>
-        <v>14907.170833333334</v>
+        <v>15971.96875</v>
       </c>
       <c r="AA49" s="12">
         <f t="shared" si="29"/>
@@ -10657,11 +10733,11 @@
       </c>
       <c r="AB49" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>13558.416666666668</v>
+        <v>14526.875</v>
       </c>
       <c r="AC49" s="12">
         <f t="shared" ca="1" si="2"/>
-        <v>1348.7541666666657</v>
+        <v>1445.09375</v>
       </c>
     </row>
     <row r="50" spans="2:29" x14ac:dyDescent="0.3">
@@ -10707,12 +10783,12 @@
       </c>
       <c r="O50" s="18">
         <f t="shared" ca="1" si="24"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P50" s="18"/>
       <c r="Q50" s="3">
         <f t="shared" ca="1" si="25"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R50" s="3" t="str">
         <f>VLOOKUP(I50, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -10726,13 +10802,13 @@
       <c r="U50" s="9"/>
       <c r="V50" s="8">
         <f t="shared" ca="1" si="26"/>
-        <v>33647.979166666672</v>
+        <v>32583.181250000001</v>
       </c>
       <c r="W50" s="3"/>
       <c r="X50" s="11"/>
       <c r="Z50" s="12">
         <f t="shared" ca="1" si="27"/>
-        <v>14907.170833333334</v>
+        <v>15971.96875</v>
       </c>
       <c r="AA50" s="12">
         <f t="shared" si="29"/>
@@ -10740,11 +10816,11 @@
       </c>
       <c r="AB50" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>13558.416666666668</v>
+        <v>14526.875</v>
       </c>
       <c r="AC50" s="12">
         <f t="shared" ca="1" si="2"/>
-        <v>1348.7541666666657</v>
+        <v>1445.09375</v>
       </c>
     </row>
     <row r="51" spans="2:29" x14ac:dyDescent="0.3">
@@ -10790,12 +10866,12 @@
       </c>
       <c r="O51" s="18">
         <f t="shared" ca="1" si="24"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P51" s="18"/>
       <c r="Q51" s="3">
         <f t="shared" ca="1" si="25"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R51" s="3" t="str">
         <f>VLOOKUP(I51, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -10809,13 +10885,13 @@
       <c r="U51" s="9"/>
       <c r="V51" s="8">
         <f t="shared" ca="1" si="26"/>
-        <v>34712.777083333334</v>
+        <v>33647.979166666672</v>
       </c>
       <c r="W51" s="3"/>
       <c r="X51" s="11"/>
       <c r="Z51" s="12">
         <f t="shared" ca="1" si="27"/>
-        <v>13842.372916666667</v>
+        <v>14907.170833333334</v>
       </c>
       <c r="AA51" s="12">
         <f t="shared" si="29"/>
@@ -10823,11 +10899,11 @@
       </c>
       <c r="AB51" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>12589.958333333334</v>
+        <v>13558.416666666668</v>
       </c>
       <c r="AC51" s="12">
         <f t="shared" ca="1" si="2"/>
-        <v>1252.4145833333332</v>
+        <v>1348.7541666666657</v>
       </c>
     </row>
     <row r="52" spans="2:29" x14ac:dyDescent="0.3">
@@ -10909,12 +10985,12 @@
       </c>
       <c r="O53" s="18">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P53" s="18"/>
       <c r="Q53" s="3">
         <f ca="1">(YEAR(O53) - YEAR(M53)) * 12 + MONTH(O53) - MONTH(M53) + 1</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R53" s="3" t="str">
         <f>VLOOKUP(I53, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -10928,13 +11004,13 @@
       <c r="U53" s="9"/>
       <c r="V53" s="8">
         <f ca="1">L53-(C53*Q53)</f>
-        <v>34813.358333333337</v>
+        <v>33739.416666666664</v>
       </c>
       <c r="W53" s="3"/>
       <c r="X53" s="11"/>
       <c r="Z53" s="12">
         <f ca="1">Q53*C53</f>
-        <v>13961.241666666665</v>
+        <v>15035.183333333332</v>
       </c>
       <c r="AA53" s="12">
         <f>(J53-F53)/24</f>
@@ -10942,21 +11018,21 @@
       </c>
       <c r="AB53" s="12">
         <f t="shared" ca="1" si="0"/>
-        <v>12703.166666666666</v>
+        <v>13680.333333333332</v>
       </c>
       <c r="AC53" s="12">
         <f t="shared" ca="1" si="2"/>
-        <v>1258.0749999999989</v>
+        <v>1354.8500000000004</v>
       </c>
     </row>
     <row r="55" spans="2:29" x14ac:dyDescent="0.3">
       <c r="L55" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="V55" s="46" t="s">
+      <c r="V55" s="48" t="s">
         <v>79</v>
       </c>
-      <c r="W55" s="46"/>
+      <c r="W55" s="48"/>
       <c r="Y55" s="7" t="s">
         <v>80</v>
       </c>
@@ -10994,7 +11070,7 @@
       <c r="Y56" s="5"/>
       <c r="Z56" s="37">
         <f ca="1">SUM(Z5:Z20)+SUM(Z35:Z53)</f>
-        <v>379819.86208333337</v>
+        <v>399025.565</v>
       </c>
     </row>
     <row r="57" spans="2:29" x14ac:dyDescent="0.3">
@@ -11260,12 +11336,12 @@
       </c>
       <c r="O62" s="18">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P62" s="18"/>
       <c r="Q62" s="3">
         <f t="shared" ca="1" si="30"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R62" s="3" t="str">
         <f>VLOOKUP(I62, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -11294,11 +11370,11 @@
       </c>
       <c r="AB62" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>15158.111111111108</v>
+        <v>15699.472222222219</v>
       </c>
       <c r="AC62" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-15158.111111111108</v>
+        <v>-15699.472222222219</v>
       </c>
     </row>
     <row r="63" spans="2:29" x14ac:dyDescent="0.3">
@@ -12089,12 +12165,12 @@
       </c>
       <c r="O78" s="18">
         <f t="shared" ref="O78:O104" ca="1" si="44">TODAY()</f>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P78" s="18"/>
       <c r="Q78" s="3">
         <f t="shared" ref="Q78:Q104" ca="1" si="45">(YEAR(O78) - YEAR(M78)) * 12 + MONTH(O78) - MONTH(M78) + 1</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R78" s="3" t="str">
         <f>VLOOKUP(I78, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -12123,11 +12199,11 @@
       </c>
       <c r="AB78" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="AC78" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-11521.396825396825</v>
+        <v>-12241.484126984127</v>
       </c>
     </row>
     <row r="79" spans="9:29" x14ac:dyDescent="0.3">
@@ -12153,12 +12229,12 @@
       </c>
       <c r="O79" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P79" s="18"/>
       <c r="Q79" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R79" s="3" t="str">
         <f>VLOOKUP(I79, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -12187,11 +12263,11 @@
       </c>
       <c r="AB79" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="AC79" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-11521.396825396825</v>
+        <v>-12241.484126984127</v>
       </c>
     </row>
     <row r="80" spans="9:29" x14ac:dyDescent="0.3">
@@ -12217,12 +12293,12 @@
       </c>
       <c r="O80" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P80" s="18"/>
       <c r="Q80" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R80" s="3" t="str">
         <f>VLOOKUP(I80, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -12251,11 +12327,11 @@
       </c>
       <c r="AB80" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="AC80" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-11521.396825396825</v>
+        <v>-12241.484126984127</v>
       </c>
     </row>
     <row r="81" spans="9:29" x14ac:dyDescent="0.3">
@@ -12281,12 +12357,12 @@
       </c>
       <c r="O81" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P81" s="18"/>
       <c r="Q81" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R81" s="3" t="str">
         <f>VLOOKUP(I81, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -12315,11 +12391,11 @@
       </c>
       <c r="AB81" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="AC81" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-11521.396825396825</v>
+        <v>-12241.484126984127</v>
       </c>
     </row>
     <row r="82" spans="9:29" x14ac:dyDescent="0.3">
@@ -12345,12 +12421,12 @@
       </c>
       <c r="O82" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P82" s="18"/>
       <c r="Q82" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R82" s="3" t="str">
         <f>VLOOKUP(I82, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -12379,11 +12455,11 @@
       </c>
       <c r="AB82" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="AC82" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-11521.396825396825</v>
+        <v>-12241.484126984127</v>
       </c>
     </row>
     <row r="83" spans="9:29" x14ac:dyDescent="0.3">
@@ -12409,12 +12485,12 @@
       </c>
       <c r="O83" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P83" s="18"/>
       <c r="Q83" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R83" s="3" t="str">
         <f>VLOOKUP(I83, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -12443,11 +12519,11 @@
       </c>
       <c r="AB83" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="AC83" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-11521.396825396825</v>
+        <v>-12241.484126984127</v>
       </c>
     </row>
     <row r="84" spans="9:29" x14ac:dyDescent="0.3">
@@ -12473,12 +12549,12 @@
       </c>
       <c r="O84" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P84" s="18"/>
       <c r="Q84" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R84" s="3" t="str">
         <f>VLOOKUP(I84, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -12507,11 +12583,11 @@
       </c>
       <c r="AB84" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="AC84" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-11521.396825396825</v>
+        <v>-12241.484126984127</v>
       </c>
     </row>
     <row r="85" spans="9:29" x14ac:dyDescent="0.3">
@@ -12537,12 +12613,12 @@
       </c>
       <c r="O85" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P85" s="18"/>
       <c r="Q85" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R85" s="3" t="str">
         <f>VLOOKUP(I85, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -12571,11 +12647,11 @@
       </c>
       <c r="AB85" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="AC85" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-11521.396825396825</v>
+        <v>-12241.484126984127</v>
       </c>
     </row>
     <row r="86" spans="9:29" x14ac:dyDescent="0.3">
@@ -12601,12 +12677,12 @@
       </c>
       <c r="O86" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P86" s="18"/>
       <c r="Q86" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R86" s="3" t="str">
         <f>VLOOKUP(I86, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -12635,11 +12711,11 @@
       </c>
       <c r="AB86" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="AC86" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-11521.396825396825</v>
+        <v>-12241.484126984127</v>
       </c>
     </row>
     <row r="87" spans="9:29" x14ac:dyDescent="0.3">
@@ -12665,12 +12741,12 @@
       </c>
       <c r="O87" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P87" s="18"/>
       <c r="Q87" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R87" s="3" t="str">
         <f>VLOOKUP(I87, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -12699,11 +12775,11 @@
       </c>
       <c r="AB87" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="AC87" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-11521.396825396825</v>
+        <v>-12241.484126984127</v>
       </c>
     </row>
     <row r="88" spans="9:29" x14ac:dyDescent="0.3">
@@ -12729,12 +12805,12 @@
       </c>
       <c r="O88" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P88" s="18"/>
       <c r="Q88" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R88" s="3" t="str">
         <f>VLOOKUP(I88, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -12763,11 +12839,11 @@
       </c>
       <c r="AB88" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="AC88" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-11521.396825396825</v>
+        <v>-12241.484126984127</v>
       </c>
     </row>
     <row r="89" spans="9:29" x14ac:dyDescent="0.3">
@@ -12793,12 +12869,12 @@
       </c>
       <c r="O89" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P89" s="18"/>
       <c r="Q89" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R89" s="3" t="str">
         <f>VLOOKUP(I89, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -12827,11 +12903,11 @@
       </c>
       <c r="AB89" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="AC89" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-11521.396825396825</v>
+        <v>-12241.484126984127</v>
       </c>
     </row>
     <row r="90" spans="9:29" x14ac:dyDescent="0.3">
@@ -12857,12 +12933,12 @@
       </c>
       <c r="O90" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P90" s="18"/>
       <c r="Q90" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R90" s="3" t="str">
         <f>VLOOKUP(I90, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -12891,11 +12967,11 @@
       </c>
       <c r="AB90" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="AC90" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-11521.396825396825</v>
+        <v>-12241.484126984127</v>
       </c>
     </row>
     <row r="91" spans="9:29" x14ac:dyDescent="0.3">
@@ -12921,12 +12997,12 @@
       </c>
       <c r="O91" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P91" s="18"/>
       <c r="Q91" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R91" s="3" t="str">
         <f>VLOOKUP(I91, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -12955,11 +13031,11 @@
       </c>
       <c r="AB91" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>12241.484126984127</v>
+        <v>12961.571428571428</v>
       </c>
       <c r="AC91" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-12241.484126984127</v>
+        <v>-12961.571428571428</v>
       </c>
     </row>
     <row r="92" spans="9:29" x14ac:dyDescent="0.3">
@@ -12985,12 +13061,12 @@
       </c>
       <c r="O92" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P92" s="18"/>
       <c r="Q92" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R92" s="3" t="str">
         <f>VLOOKUP(I92, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -13019,11 +13095,11 @@
       </c>
       <c r="AB92" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>12241.484126984127</v>
+        <v>12961.571428571428</v>
       </c>
       <c r="AC92" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-12241.484126984127</v>
+        <v>-12961.571428571428</v>
       </c>
     </row>
     <row r="93" spans="9:29" x14ac:dyDescent="0.3">
@@ -13049,12 +13125,12 @@
       </c>
       <c r="O93" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P93" s="18"/>
       <c r="Q93" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R93" s="3" t="str">
         <f>VLOOKUP(I93, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -13083,11 +13159,11 @@
       </c>
       <c r="AB93" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>12241.484126984127</v>
+        <v>12961.571428571428</v>
       </c>
       <c r="AC93" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-12241.484126984127</v>
+        <v>-12961.571428571428</v>
       </c>
     </row>
     <row r="94" spans="9:29" x14ac:dyDescent="0.3">
@@ -13113,12 +13189,12 @@
       </c>
       <c r="O94" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P94" s="18"/>
       <c r="Q94" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R94" s="3" t="str">
         <f>VLOOKUP(I94, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -13147,11 +13223,11 @@
       </c>
       <c r="AB94" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>12241.484126984127</v>
+        <v>12961.571428571428</v>
       </c>
       <c r="AC94" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-12241.484126984127</v>
+        <v>-12961.571428571428</v>
       </c>
     </row>
     <row r="95" spans="9:29" x14ac:dyDescent="0.3">
@@ -13177,12 +13253,12 @@
       </c>
       <c r="O95" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P95" s="18"/>
       <c r="Q95" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R95" s="3" t="str">
         <f>VLOOKUP(I95, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -13211,11 +13287,11 @@
       </c>
       <c r="AB95" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>12241.484126984127</v>
+        <v>12961.571428571428</v>
       </c>
       <c r="AC95" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-12241.484126984127</v>
+        <v>-12961.571428571428</v>
       </c>
     </row>
     <row r="96" spans="9:29" x14ac:dyDescent="0.3">
@@ -13241,12 +13317,12 @@
       </c>
       <c r="O96" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P96" s="18"/>
       <c r="Q96" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R96" s="3" t="str">
         <f>VLOOKUP(I96, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -13275,11 +13351,11 @@
       </c>
       <c r="AB96" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>12241.484126984127</v>
+        <v>12961.571428571428</v>
       </c>
       <c r="AC96" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-12241.484126984127</v>
+        <v>-12961.571428571428</v>
       </c>
     </row>
     <row r="97" spans="9:29" x14ac:dyDescent="0.3">
@@ -13305,12 +13381,12 @@
       </c>
       <c r="O97" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P97" s="18"/>
       <c r="Q97" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R97" s="3" t="str">
         <f>VLOOKUP(I97, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -13339,11 +13415,11 @@
       </c>
       <c r="AB97" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>12241.484126984127</v>
+        <v>12961.571428571428</v>
       </c>
       <c r="AC97" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-12241.484126984127</v>
+        <v>-12961.571428571428</v>
       </c>
     </row>
     <row r="98" spans="9:29" x14ac:dyDescent="0.3">
@@ -13369,12 +13445,12 @@
       </c>
       <c r="O98" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P98" s="18"/>
       <c r="Q98" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R98" s="3" t="str">
         <f>VLOOKUP(I98, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -13403,11 +13479,11 @@
       </c>
       <c r="AB98" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>12241.484126984127</v>
+        <v>12961.571428571428</v>
       </c>
       <c r="AC98" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-12241.484126984127</v>
+        <v>-12961.571428571428</v>
       </c>
     </row>
     <row r="99" spans="9:29" x14ac:dyDescent="0.3">
@@ -13433,12 +13509,12 @@
       </c>
       <c r="O99" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P99" s="18"/>
       <c r="Q99" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R99" s="3" t="str">
         <f>VLOOKUP(I99, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -13467,11 +13543,11 @@
       </c>
       <c r="AB99" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="AC99" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-11521.396825396825</v>
+        <v>-12241.484126984127</v>
       </c>
     </row>
     <row r="100" spans="9:29" x14ac:dyDescent="0.3">
@@ -13497,12 +13573,12 @@
       </c>
       <c r="O100" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P100" s="18"/>
       <c r="Q100" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R100" s="3" t="str">
         <f>VLOOKUP(I100, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -13531,11 +13607,11 @@
       </c>
       <c r="AB100" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="AC100" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-11521.396825396825</v>
+        <v>-12241.484126984127</v>
       </c>
     </row>
     <row r="101" spans="9:29" x14ac:dyDescent="0.3">
@@ -13561,12 +13637,12 @@
       </c>
       <c r="O101" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P101" s="18"/>
       <c r="Q101" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R101" s="3" t="str">
         <f>VLOOKUP(I101, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -13595,11 +13671,11 @@
       </c>
       <c r="AB101" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="AC101" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-11521.396825396825</v>
+        <v>-12241.484126984127</v>
       </c>
     </row>
     <row r="102" spans="9:29" x14ac:dyDescent="0.3">
@@ -13625,12 +13701,12 @@
       </c>
       <c r="O102" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P102" s="18"/>
       <c r="Q102" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R102" s="3" t="str">
         <f>VLOOKUP(I102, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -13659,11 +13735,11 @@
       </c>
       <c r="AB102" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="AC102" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-11521.396825396825</v>
+        <v>-12241.484126984127</v>
       </c>
     </row>
     <row r="103" spans="9:29" x14ac:dyDescent="0.3">
@@ -13689,12 +13765,12 @@
       </c>
       <c r="O103" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P103" s="18"/>
       <c r="Q103" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R103" s="3" t="str">
         <f>VLOOKUP(I103, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -13723,11 +13799,11 @@
       </c>
       <c r="AB103" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="AC103" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-11521.396825396825</v>
+        <v>-12241.484126984127</v>
       </c>
     </row>
     <row r="104" spans="9:29" x14ac:dyDescent="0.3">
@@ -13753,12 +13829,12 @@
       </c>
       <c r="O104" s="18">
         <f t="shared" ca="1" si="44"/>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P104" s="18"/>
       <c r="Q104" s="3">
         <f t="shared" ca="1" si="45"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R104" s="3" t="str">
         <f>VLOOKUP(I104, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -13787,11 +13863,11 @@
       </c>
       <c r="AB104" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="AC104" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-11521.396825396825</v>
+        <v>-12241.484126984127</v>
       </c>
     </row>
     <row r="105" spans="9:29" x14ac:dyDescent="0.3">
@@ -13958,12 +14034,12 @@
       </c>
       <c r="O109" s="18">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P109" s="18"/>
       <c r="Q109" s="3">
         <f ca="1">(YEAR(O109) - YEAR(M109)) * 12 + MONTH(O109) - MONTH(M109) + 1</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R109" s="3" t="str">
         <f>VLOOKUP(I109, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -13992,11 +14068,11 @@
       </c>
       <c r="AB109" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>32968.730158730155</v>
+        <v>35029.275793650791</v>
       </c>
       <c r="AC109" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-32968.730158730155</v>
+        <v>-35029.275793650791</v>
       </c>
     </row>
     <row r="110" spans="9:29" x14ac:dyDescent="0.3">
@@ -14022,12 +14098,12 @@
       </c>
       <c r="O110" s="18">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P110" s="18"/>
       <c r="Q110" s="3">
         <f ca="1">(YEAR(O110) - YEAR(M110)) * 12 + MONTH(O110) - MONTH(M110) + 1</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R110" s="3" t="str">
         <f>VLOOKUP(I110, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -14056,11 +14132,11 @@
       </c>
       <c r="AB110" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>32968.730158730155</v>
+        <v>35029.275793650791</v>
       </c>
       <c r="AC110" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-32968.730158730155</v>
+        <v>-35029.275793650791</v>
       </c>
     </row>
     <row r="111" spans="9:29" x14ac:dyDescent="0.3">
@@ -14086,12 +14162,12 @@
       </c>
       <c r="O111" s="18">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P111" s="18"/>
       <c r="Q111" s="3">
         <f ca="1">(YEAR(O111) - YEAR(M111)) * 12 + MONTH(O111) - MONTH(M111) + 1</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R111" s="3" t="str">
         <f>VLOOKUP(I111, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -14120,11 +14196,11 @@
       </c>
       <c r="AB111" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>32968.730158730155</v>
+        <v>35029.275793650791</v>
       </c>
       <c r="AC111" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-32968.730158730155</v>
+        <v>-35029.275793650791</v>
       </c>
     </row>
     <row r="112" spans="9:29" x14ac:dyDescent="0.3">
@@ -14150,12 +14226,12 @@
       </c>
       <c r="O112" s="18">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P112" s="18"/>
       <c r="Q112" s="3">
         <f ca="1">(YEAR(O112) - YEAR(M112)) * 12 + MONTH(O112) - MONTH(M112) + 1</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R112" s="3" t="str">
         <f>VLOOKUP(I112, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -14184,11 +14260,11 @@
       </c>
       <c r="AB112" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>32968.730158730155</v>
+        <v>35029.275793650791</v>
       </c>
       <c r="AC112" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-32968.730158730155</v>
+        <v>-35029.275793650791</v>
       </c>
     </row>
     <row r="113" spans="9:29" x14ac:dyDescent="0.3">
@@ -14214,12 +14290,12 @@
       </c>
       <c r="O113" s="18">
         <f ca="1">TODAY()</f>
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="P113" s="18"/>
       <c r="Q113" s="3">
         <f ca="1">(YEAR(O113) - YEAR(M113)) * 12 + MONTH(O113) - MONTH(M113) + 1</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R113" s="3" t="str">
         <f>VLOOKUP(I113, [1]Fleet!$C:$V, 20, FALSE)</f>
@@ -14248,11 +14324,11 @@
       </c>
       <c r="AB113" s="42">
         <f t="shared" ca="1" si="32"/>
-        <v>32968.730158730155</v>
+        <v>35029.275793650791</v>
       </c>
       <c r="AC113" s="42">
         <f t="shared" ca="1" si="33"/>
-        <v>-32968.730158730155</v>
+        <v>-35029.275793650791</v>
       </c>
     </row>
     <row r="114" spans="9:29" x14ac:dyDescent="0.3">
@@ -15789,11 +15865,11 @@
       </c>
       <c r="P27" s="44">
         <f ca="1">+VLOOKUP(B27,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>14713.666666666672</v>
+        <v>15239.154761904767</v>
       </c>
       <c r="Q27" s="44">
         <f ca="1">+O27-P27</f>
-        <v>27898.047619047618</v>
+        <v>27372.559523809523</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.3">
@@ -16021,11 +16097,11 @@
       </c>
       <c r="P32" s="44">
         <f ca="1">+VLOOKUP(B32,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>15158.111111111108</v>
+        <v>15699.472222222219</v>
       </c>
       <c r="Q32" s="44">
         <f ca="1">+O32-P32</f>
-        <v>27834.555555555555</v>
+        <v>27293.194444444445</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.3">
@@ -16385,11 +16461,11 @@
       </c>
       <c r="P40" s="44">
         <f ca="1">+VLOOKUP(B40,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>18213.661666666663</v>
+        <v>18864.149583333332</v>
       </c>
       <c r="Q40" s="44">
         <f ca="1">+O40-P40</f>
-        <v>27398.048333333336</v>
+        <v>26747.560416666667</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
@@ -16485,11 +16561,11 @@
       </c>
       <c r="P42" s="44">
         <f ca="1">+VLOOKUP(B42,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="Q42" s="44">
         <f t="shared" ref="Q42:Q84" ca="1" si="1">+O42-P42</f>
-        <v>33260.69841269841</v>
+        <v>32540.611111111109</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.3">
@@ -16541,11 +16617,11 @@
       </c>
       <c r="P43" s="44">
         <f ca="1">+VLOOKUP(B43,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="Q43" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>33260.69841269841</v>
+        <v>32540.611111111109</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.3">
@@ -16597,11 +16673,11 @@
       </c>
       <c r="P44" s="44">
         <f ca="1">+VLOOKUP(B44,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="Q44" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>33260.69841269841</v>
+        <v>32540.611111111109</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
@@ -16653,11 +16729,11 @@
       </c>
       <c r="P45" s="44">
         <f ca="1">+VLOOKUP(B45,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="Q45" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>33260.69841269841</v>
+        <v>32540.611111111109</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.3">
@@ -16709,11 +16785,11 @@
       </c>
       <c r="P46" s="44">
         <f ca="1">+VLOOKUP(B46,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="Q46" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>33260.69841269841</v>
+        <v>32540.611111111109</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.3">
@@ -16765,11 +16841,11 @@
       </c>
       <c r="P47" s="44">
         <f ca="1">+VLOOKUP(B47,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="Q47" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>33260.69841269841</v>
+        <v>32540.611111111109</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.3">
@@ -16821,11 +16897,11 @@
       </c>
       <c r="P48" s="44">
         <f ca="1">+VLOOKUP(B48,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="Q48" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>33260.69841269841</v>
+        <v>32540.611111111109</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.3">
@@ -16877,11 +16953,11 @@
       </c>
       <c r="P49" s="44">
         <f ca="1">+VLOOKUP(B49,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="Q49" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>33260.69841269841</v>
+        <v>32540.611111111109</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.3">
@@ -16933,11 +17009,11 @@
       </c>
       <c r="P50" s="44">
         <f ca="1">+VLOOKUP(B50,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="Q50" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>33260.69841269841</v>
+        <v>32540.611111111109</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.3">
@@ -16989,11 +17065,11 @@
       </c>
       <c r="P51" s="44">
         <f ca="1">+VLOOKUP(B51,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="Q51" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>33260.69841269841</v>
+        <v>32540.611111111109</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.3">
@@ -17045,11 +17121,11 @@
       </c>
       <c r="P52" s="44">
         <f ca="1">+VLOOKUP(B52,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="Q52" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>33260.69841269841</v>
+        <v>32540.611111111109</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.3">
@@ -17101,11 +17177,11 @@
       </c>
       <c r="P53" s="44">
         <f ca="1">+VLOOKUP(B53,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="Q53" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>33260.69841269841</v>
+        <v>32540.611111111109</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.3">
@@ -17157,11 +17233,11 @@
       </c>
       <c r="P54" s="44">
         <f ca="1">+VLOOKUP(B54,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="Q54" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>33260.69841269841</v>
+        <v>32540.611111111109</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.3">
@@ -17213,11 +17289,11 @@
       </c>
       <c r="P55" s="44">
         <f ca="1">+VLOOKUP(B55,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>12241.484126984127</v>
+        <v>12961.571428571428</v>
       </c>
       <c r="Q55" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>32540.611111111109</v>
+        <v>31820.523809523809</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.3">
@@ -17269,11 +17345,11 @@
       </c>
       <c r="P56" s="44">
         <f ca="1">+VLOOKUP(B56,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>12241.484126984127</v>
+        <v>12961.571428571428</v>
       </c>
       <c r="Q56" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>32540.611111111109</v>
+        <v>31820.523809523809</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.3">
@@ -17325,11 +17401,11 @@
       </c>
       <c r="P57" s="44">
         <f ca="1">+VLOOKUP(B57,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>12241.484126984127</v>
+        <v>12961.571428571428</v>
       </c>
       <c r="Q57" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>32540.611111111109</v>
+        <v>31820.523809523809</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.3">
@@ -17381,11 +17457,11 @@
       </c>
       <c r="P58" s="44">
         <f ca="1">+VLOOKUP(B58,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>12241.484126984127</v>
+        <v>12961.571428571428</v>
       </c>
       <c r="Q58" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>32540.611111111109</v>
+        <v>31820.523809523809</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.3">
@@ -17437,11 +17513,11 @@
       </c>
       <c r="P59" s="44">
         <f ca="1">+VLOOKUP(B59,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>12241.484126984127</v>
+        <v>12961.571428571428</v>
       </c>
       <c r="Q59" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>32540.611111111109</v>
+        <v>31820.523809523809</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.3">
@@ -17493,11 +17569,11 @@
       </c>
       <c r="P60" s="44">
         <f ca="1">+VLOOKUP(B60,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>12241.484126984127</v>
+        <v>12961.571428571428</v>
       </c>
       <c r="Q60" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>32540.611111111109</v>
+        <v>31820.523809523809</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.3">
@@ -17549,11 +17625,11 @@
       </c>
       <c r="P61" s="44">
         <f ca="1">+VLOOKUP(B61,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>12241.484126984127</v>
+        <v>12961.571428571428</v>
       </c>
       <c r="Q61" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>32540.611111111109</v>
+        <v>31820.523809523809</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.3">
@@ -17605,11 +17681,11 @@
       </c>
       <c r="P62" s="44">
         <f ca="1">+VLOOKUP(B62,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>12241.484126984127</v>
+        <v>12961.571428571428</v>
       </c>
       <c r="Q62" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>32540.611111111109</v>
+        <v>31820.523809523809</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.3">
@@ -17661,11 +17737,11 @@
       </c>
       <c r="P63" s="44">
         <f ca="1">+VLOOKUP(B63,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="Q63" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>33260.69841269841</v>
+        <v>32540.611111111109</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.3">
@@ -17717,11 +17793,11 @@
       </c>
       <c r="P64" s="44">
         <f ca="1">+VLOOKUP(B64,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="Q64" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>33260.69841269841</v>
+        <v>32540.611111111109</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.3">
@@ -17773,11 +17849,11 @@
       </c>
       <c r="P65" s="44">
         <f ca="1">+VLOOKUP(B65,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="Q65" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>33260.69841269841</v>
+        <v>32540.611111111109</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.3">
@@ -17829,11 +17905,11 @@
       </c>
       <c r="P66" s="44">
         <f ca="1">+VLOOKUP(B66,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="Q66" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>33260.69841269841</v>
+        <v>32540.611111111109</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.3">
@@ -17885,11 +17961,11 @@
       </c>
       <c r="P67" s="44">
         <f ca="1">+VLOOKUP(B67,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="Q67" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>33260.69841269841</v>
+        <v>32540.611111111109</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.3">
@@ -17941,11 +18017,11 @@
       </c>
       <c r="P68" s="44">
         <f ca="1">+VLOOKUP(B68,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>11521.396825396825</v>
+        <v>12241.484126984127</v>
       </c>
       <c r="Q68" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>33260.69841269841</v>
+        <v>32540.611111111109</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.3">
@@ -17997,11 +18073,11 @@
       </c>
       <c r="P69" s="44">
         <f ca="1">+VLOOKUP(B69,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>13690.833333333332</v>
+        <v>14668.75</v>
       </c>
       <c r="Q69" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>32079.166666666668</v>
+        <v>31101.25</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.3">
@@ -18053,11 +18129,11 @@
       </c>
       <c r="P70" s="44">
         <f ca="1">+VLOOKUP(B70,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>13690.833333333332</v>
+        <v>14668.75</v>
       </c>
       <c r="Q70" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>32079.166666666668</v>
+        <v>31101.25</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.3">
@@ -18109,11 +18185,11 @@
       </c>
       <c r="P71" s="44">
         <f ca="1">+VLOOKUP(B71,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>13690.833333333332</v>
+        <v>14668.75</v>
       </c>
       <c r="Q71" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>32079.166666666668</v>
+        <v>31101.25</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.3">
@@ -18165,11 +18241,11 @@
       </c>
       <c r="P72" s="44">
         <f ca="1">+VLOOKUP(B72,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>13558.416666666668</v>
+        <v>14526.875</v>
       </c>
       <c r="Q72" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>32684.583333333332</v>
+        <v>31716.125</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.3">
@@ -18221,11 +18297,11 @@
       </c>
       <c r="P73" s="44">
         <f ca="1">+VLOOKUP(B73,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>13558.416666666668</v>
+        <v>14526.875</v>
       </c>
       <c r="Q73" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>32684.583333333332</v>
+        <v>31716.125</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.3">
@@ -18277,11 +18353,11 @@
       </c>
       <c r="P74" s="44">
         <f ca="1">+VLOOKUP(B74,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>13690.833333333332</v>
+        <v>14668.75</v>
       </c>
       <c r="Q74" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>32079.166666666668</v>
+        <v>31101.25</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.3">
@@ -18333,11 +18409,11 @@
       </c>
       <c r="P75" s="44">
         <f ca="1">+VLOOKUP(B75,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>13690.833333333332</v>
+        <v>14668.75</v>
       </c>
       <c r="Q75" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>32079.166666666668</v>
+        <v>31101.25</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.3">
@@ -18389,11 +18465,11 @@
       </c>
       <c r="P76" s="44">
         <f ca="1">+VLOOKUP(B76,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>13558.416666666668</v>
+        <v>14526.875</v>
       </c>
       <c r="Q76" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>32684.583333333332</v>
+        <v>31716.125</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.3">
@@ -18445,11 +18521,11 @@
       </c>
       <c r="P77" s="44">
         <f ca="1">+VLOOKUP(B77,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>13558.416666666668</v>
+        <v>14526.875</v>
       </c>
       <c r="Q77" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>32684.583333333332</v>
+        <v>31716.125</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.3">
@@ -18501,11 +18577,11 @@
       </c>
       <c r="P78" s="44">
         <f ca="1">+VLOOKUP(B78,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>13690.833333333332</v>
+        <v>14668.75</v>
       </c>
       <c r="Q78" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>32079.166666666668</v>
+        <v>31101.25</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.3">
@@ -18557,11 +18633,11 @@
       </c>
       <c r="P79" s="44">
         <f ca="1">+VLOOKUP(B79,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>13558.416666666668</v>
+        <v>14526.875</v>
       </c>
       <c r="Q79" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>32684.583333333332</v>
+        <v>31716.125</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.3">
@@ -18613,11 +18689,11 @@
       </c>
       <c r="P80" s="44">
         <f ca="1">+VLOOKUP(B80,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>13558.416666666668</v>
+        <v>14526.875</v>
       </c>
       <c r="Q80" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>32684.583333333332</v>
+        <v>31716.125</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.3">
@@ -18669,11 +18745,11 @@
       </c>
       <c r="P81" s="44">
         <f ca="1">+VLOOKUP(B81,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>12589.958333333334</v>
+        <v>13558.416666666668</v>
       </c>
       <c r="Q81" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>33653.041666666664</v>
+        <v>32684.583333333332</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.3">
@@ -18725,11 +18801,11 @@
       </c>
       <c r="P82" s="44">
         <f ca="1">+VLOOKUP(B82,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>12712.916666666666</v>
+        <v>13690.833333333332</v>
       </c>
       <c r="Q82" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>33057.083333333336</v>
+        <v>32079.166666666668</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.3">
@@ -18781,11 +18857,11 @@
       </c>
       <c r="P83" s="44">
         <f ca="1">+VLOOKUP(B83,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>12589.958333333334</v>
+        <v>13558.416666666668</v>
       </c>
       <c r="Q83" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>33653.041666666664</v>
+        <v>32684.583333333332</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.3">
@@ -18837,11 +18913,11 @@
       </c>
       <c r="P84" s="44">
         <f ca="1">+VLOOKUP(B84,'Dep TCCI'!$I$3:$AC$117,20,FALSE)</f>
-        <v>12703.166666666666</v>
+        <v>13680.333333333332</v>
       </c>
       <c r="Q84" s="44">
         <f t="shared" ca="1" si="1"/>
-        <v>33748.833333333336</v>
+        <v>32771.666666666672</v>
       </c>
     </row>
   </sheetData>
@@ -18852,6 +18928,447 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98486050-40FA-49D5-9FB9-332ADC324603}">
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.44140625" customWidth="1"/>
+    <col min="2" max="2" width="26.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="8" width="17.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="47" t="s">
+        <v>262</v>
+      </c>
+      <c r="C1" s="47" t="s">
+        <v>248</v>
+      </c>
+      <c r="D1" s="47" t="s">
+        <v>249</v>
+      </c>
+      <c r="E1" s="47" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="47">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="49" t="s">
+        <v>250</v>
+      </c>
+      <c r="C2" s="46">
+        <v>47</v>
+      </c>
+      <c r="D2" s="46">
+        <v>5</v>
+      </c>
+      <c r="E2" s="46">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="47">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="49" t="s">
+        <v>251</v>
+      </c>
+      <c r="C3" s="46">
+        <v>49</v>
+      </c>
+      <c r="D3" s="46">
+        <v>3</v>
+      </c>
+      <c r="E3" s="46">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="47">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="49" t="s">
+        <v>252</v>
+      </c>
+      <c r="C4" s="46">
+        <v>49</v>
+      </c>
+      <c r="D4" s="46">
+        <v>3</v>
+      </c>
+      <c r="E4" s="46">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="47">
+        <v>2025</v>
+      </c>
+      <c r="B5" s="49" t="s">
+        <v>253</v>
+      </c>
+      <c r="C5" s="46">
+        <v>46</v>
+      </c>
+      <c r="D5" s="46">
+        <v>6</v>
+      </c>
+      <c r="E5" s="46">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="47">
+        <v>2025</v>
+      </c>
+      <c r="B6" s="49" t="s">
+        <v>254</v>
+      </c>
+      <c r="C6" s="46">
+        <v>44</v>
+      </c>
+      <c r="D6" s="46">
+        <v>8</v>
+      </c>
+      <c r="E6" s="46">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="47">
+        <v>2025</v>
+      </c>
+      <c r="B7" s="49" t="s">
+        <v>255</v>
+      </c>
+      <c r="C7" s="46">
+        <v>46</v>
+      </c>
+      <c r="D7" s="46">
+        <v>6</v>
+      </c>
+      <c r="E7" s="46">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="47">
+        <v>2025</v>
+      </c>
+      <c r="B8" s="49" t="s">
+        <v>256</v>
+      </c>
+      <c r="C8" s="46">
+        <v>45</v>
+      </c>
+      <c r="D8" s="46">
+        <v>7</v>
+      </c>
+      <c r="E8" s="46">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="47">
+        <v>2025</v>
+      </c>
+      <c r="B9" s="49" t="s">
+        <v>257</v>
+      </c>
+      <c r="C9" s="46">
+        <v>43</v>
+      </c>
+      <c r="D9" s="46">
+        <v>9</v>
+      </c>
+      <c r="E9" s="46">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="47">
+        <v>2025</v>
+      </c>
+      <c r="B10" s="49" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" s="46">
+        <v>45</v>
+      </c>
+      <c r="D10" s="46">
+        <v>7</v>
+      </c>
+      <c r="E10" s="46">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="47">
+        <v>2025</v>
+      </c>
+      <c r="B11" s="49" t="s">
+        <v>259</v>
+      </c>
+      <c r="C11" s="46">
+        <v>45</v>
+      </c>
+      <c r="D11" s="46">
+        <v>7</v>
+      </c>
+      <c r="E11" s="46">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="47">
+        <v>2025</v>
+      </c>
+      <c r="B12" s="49" t="s">
+        <v>260</v>
+      </c>
+      <c r="C12" s="46">
+        <v>47</v>
+      </c>
+      <c r="D12" s="46">
+        <v>5</v>
+      </c>
+      <c r="E12" s="46">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="47">
+        <v>2025</v>
+      </c>
+      <c r="B13" s="49" t="s">
+        <v>261</v>
+      </c>
+      <c r="C13" s="46">
+        <v>44</v>
+      </c>
+      <c r="D13" s="46">
+        <v>8</v>
+      </c>
+      <c r="E13" s="46">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="47">
+        <v>2025</v>
+      </c>
+      <c r="B14" s="49" t="s">
+        <v>250</v>
+      </c>
+      <c r="C14" s="46">
+        <v>34</v>
+      </c>
+      <c r="D14" s="46">
+        <v>18</v>
+      </c>
+      <c r="E14" s="46">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="47">
+        <v>2025</v>
+      </c>
+      <c r="B15" s="49" t="s">
+        <v>251</v>
+      </c>
+      <c r="C15" s="46">
+        <v>36</v>
+      </c>
+      <c r="D15" s="46">
+        <v>21</v>
+      </c>
+      <c r="E15" s="46">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="47">
+        <v>2025</v>
+      </c>
+      <c r="B16" s="49" t="s">
+        <v>252</v>
+      </c>
+      <c r="C16" s="46">
+        <v>45</v>
+      </c>
+      <c r="D16" s="46">
+        <v>12</v>
+      </c>
+      <c r="E16" s="46">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="47">
+        <v>2024</v>
+      </c>
+      <c r="B17" s="49" t="s">
+        <v>253</v>
+      </c>
+      <c r="C17" s="46">
+        <v>22</v>
+      </c>
+      <c r="D17" s="46">
+        <v>8</v>
+      </c>
+      <c r="E17" s="46">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="47">
+        <v>2024</v>
+      </c>
+      <c r="B18" s="49" t="s">
+        <v>254</v>
+      </c>
+      <c r="C18" s="46">
+        <v>19</v>
+      </c>
+      <c r="D18" s="46">
+        <v>11</v>
+      </c>
+      <c r="E18" s="46">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="47">
+        <v>2024</v>
+      </c>
+      <c r="B19" s="49" t="s">
+        <v>255</v>
+      </c>
+      <c r="C19" s="46">
+        <v>23</v>
+      </c>
+      <c r="D19" s="46">
+        <v>7</v>
+      </c>
+      <c r="E19" s="46">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="47">
+        <v>2024</v>
+      </c>
+      <c r="B20" s="49" t="s">
+        <v>256</v>
+      </c>
+      <c r="C20" s="46">
+        <v>19</v>
+      </c>
+      <c r="D20" s="46">
+        <v>11</v>
+      </c>
+      <c r="E20" s="46">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="47">
+        <v>2024</v>
+      </c>
+      <c r="B21" s="49" t="s">
+        <v>257</v>
+      </c>
+      <c r="C21" s="46">
+        <v>22</v>
+      </c>
+      <c r="D21" s="46">
+        <v>8</v>
+      </c>
+      <c r="E21" s="46">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="47">
+        <v>2024</v>
+      </c>
+      <c r="B22" s="49" t="s">
+        <v>258</v>
+      </c>
+      <c r="C22" s="46">
+        <v>21</v>
+      </c>
+      <c r="D22" s="46">
+        <v>9</v>
+      </c>
+      <c r="E22" s="46">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="47">
+        <v>2024</v>
+      </c>
+      <c r="B23" s="49" t="s">
+        <v>259</v>
+      </c>
+      <c r="C23" s="46">
+        <v>17</v>
+      </c>
+      <c r="D23" s="46">
+        <v>13</v>
+      </c>
+      <c r="E23" s="46">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="47">
+        <v>2024</v>
+      </c>
+      <c r="B24" s="49" t="s">
+        <v>260</v>
+      </c>
+      <c r="C24" s="46">
+        <v>12</v>
+      </c>
+      <c r="D24" s="46">
+        <v>8</v>
+      </c>
+      <c r="E24" s="46">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="47">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="49" t="s">
+        <v>261</v>
+      </c>
+      <c r="C25" s="46">
+        <v>12</v>
+      </c>
+      <c r="D25" s="46">
+        <v>8</v>
+      </c>
+      <c r="E25" s="46">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="27" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{fcec5505-8291-4cd2-be3c-852f3a7697ca}" enabled="1" method="Standard" siteId="{8c642d1d-d709-47b0-ab10-080af10798fb}" removed="0"/>
